--- a/artfynd/A 36342-2021 artfynd.xlsx
+++ b/artfynd/A 36342-2021 artfynd.xlsx
@@ -1548,7 +1548,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128539190</v>
+        <v>128539187</v>
       </c>
       <c r="B11" t="n">
         <v>98571</v>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>725646</v>
+        <v>725549</v>
       </c>
       <c r="R11" t="n">
-        <v>7089766</v>
+        <v>7089797</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,7 +1645,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128539187</v>
+        <v>128539190</v>
       </c>
       <c r="B12" t="n">
         <v>98571</v>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>725549</v>
+        <v>725646</v>
       </c>
       <c r="R12" t="n">
-        <v>7089797</v>
+        <v>7089766</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128539188</v>
+        <v>128539177</v>
       </c>
       <c r="B16" t="n">
-        <v>98571</v>
+        <v>57845</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>725568</v>
+        <v>725639</v>
       </c>
       <c r="R16" t="n">
-        <v>7089783</v>
+        <v>7089856</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2135,32 +2135,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128539177</v>
+        <v>128539188</v>
       </c>
       <c r="B17" t="n">
-        <v>57845</v>
+        <v>98571</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>725639</v>
+        <v>725568</v>
       </c>
       <c r="R17" t="n">
-        <v>7089856</v>
+        <v>7089783</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 36342-2021 artfynd.xlsx
+++ b/artfynd/A 36342-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128539173</v>
       </c>
       <c r="B2" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128539178</v>
       </c>
       <c r="B3" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128539194</v>
       </c>
       <c r="B4" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128539172</v>
       </c>
       <c r="B5" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128539183</v>
       </c>
       <c r="B6" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128539171</v>
       </c>
       <c r="B7" t="n">
-        <v>75171</v>
+        <v>75175</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128539191</v>
       </c>
       <c r="B8" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128539184</v>
       </c>
       <c r="B9" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128539186</v>
       </c>
       <c r="B10" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128539187</v>
+        <v>128539190</v>
       </c>
       <c r="B11" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>725549</v>
+        <v>725646</v>
       </c>
       <c r="R11" t="n">
-        <v>7089797</v>
+        <v>7089766</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128539190</v>
+        <v>128539187</v>
       </c>
       <c r="B12" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>725646</v>
+        <v>725549</v>
       </c>
       <c r="R12" t="n">
-        <v>7089766</v>
+        <v>7089797</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,49 +1742,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128539182</v>
+        <v>128539193</v>
       </c>
       <c r="B13" t="n">
-        <v>98571</v>
+        <v>91476</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Storbäcken, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>725674</v>
+        <v>725525</v>
       </c>
       <c r="R13" t="n">
-        <v>7089751</v>
+        <v>7089765</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1825,7 +1821,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1847,7 +1842,7 @@
         <v>128539189</v>
       </c>
       <c r="B14" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1941,45 +1936,49 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128539193</v>
+        <v>128539182</v>
       </c>
       <c r="B15" t="n">
-        <v>91470</v>
+        <v>98579</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Storbäcken, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>725525</v>
+        <v>725674</v>
       </c>
       <c r="R15" t="n">
-        <v>7089765</v>
+        <v>7089751</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2020,6 +2019,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2041,7 +2041,7 @@
         <v>128539177</v>
       </c>
       <c r="B16" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>128539188</v>
       </c>
       <c r="B17" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>128539181</v>
       </c>
       <c r="B18" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>128539175</v>
       </c>
       <c r="B19" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>128539176</v>
       </c>
       <c r="B20" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>128539174</v>
       </c>
       <c r="B21" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 36342-2021 artfynd.xlsx
+++ b/artfynd/A 36342-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128539173</v>
       </c>
       <c r="B2" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128539172</v>
       </c>
       <c r="B5" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128539183</v>
       </c>
       <c r="B6" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128539191</v>
       </c>
       <c r="B8" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128539184</v>
       </c>
       <c r="B9" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128539186</v>
       </c>
       <c r="B10" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128539190</v>
+        <v>128539187</v>
       </c>
       <c r="B11" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>725646</v>
+        <v>725549</v>
       </c>
       <c r="R11" t="n">
-        <v>7089766</v>
+        <v>7089797</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128539187</v>
+        <v>128539190</v>
       </c>
       <c r="B12" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>725549</v>
+        <v>725646</v>
       </c>
       <c r="R12" t="n">
-        <v>7089797</v>
+        <v>7089766</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1745,7 +1745,7 @@
         <v>128539193</v>
       </c>
       <c r="B13" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128539189</v>
+        <v>128539182</v>
       </c>
       <c r="B14" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1867,17 +1867,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Storbäcken, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>725622</v>
+        <v>725674</v>
       </c>
       <c r="R14" t="n">
-        <v>7089767</v>
+        <v>7089751</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1918,6 +1922,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1936,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128539182</v>
+        <v>128539189</v>
       </c>
       <c r="B15" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1964,21 +1969,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Storbäcken, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>725674</v>
+        <v>725622</v>
       </c>
       <c r="R15" t="n">
-        <v>7089751</v>
+        <v>7089767</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2019,7 +2020,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2138,7 +2138,7 @@
         <v>128539188</v>
       </c>
       <c r="B17" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>128539181</v>
       </c>
       <c r="B18" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 36342-2021 artfynd.xlsx
+++ b/artfynd/A 36342-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128539173</v>
       </c>
       <c r="B2" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128539178</v>
       </c>
       <c r="B3" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128539194</v>
+        <v>128539172</v>
       </c>
       <c r="B4" t="n">
-        <v>82946</v>
+        <v>91466</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>725726</v>
+        <v>725582</v>
       </c>
       <c r="R4" t="n">
-        <v>7089844</v>
+        <v>7089761</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128539172</v>
+        <v>128539194</v>
       </c>
       <c r="B5" t="n">
-        <v>91464</v>
+        <v>82948</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>725582</v>
+        <v>725726</v>
       </c>
       <c r="R5" t="n">
-        <v>7089761</v>
+        <v>7089844</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
         <v>128539183</v>
       </c>
       <c r="B6" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128539171</v>
       </c>
       <c r="B7" t="n">
-        <v>75175</v>
+        <v>75177</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128539191</v>
       </c>
       <c r="B8" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128539184</v>
       </c>
       <c r="B9" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128539186</v>
       </c>
       <c r="B10" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128539187</v>
       </c>
       <c r="B11" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128539190</v>
       </c>
       <c r="B12" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128539193</v>
       </c>
       <c r="B13" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128539182</v>
       </c>
       <c r="B14" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>128539189</v>
       </c>
       <c r="B15" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128539177</v>
+        <v>128539188</v>
       </c>
       <c r="B16" t="n">
-        <v>57849</v>
+        <v>98588</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>725639</v>
+        <v>725568</v>
       </c>
       <c r="R16" t="n">
-        <v>7089856</v>
+        <v>7089783</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2135,32 +2135,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128539188</v>
+        <v>128539177</v>
       </c>
       <c r="B17" t="n">
-        <v>98585</v>
+        <v>57849</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>725568</v>
+        <v>725639</v>
       </c>
       <c r="R17" t="n">
-        <v>7089783</v>
+        <v>7089856</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2235,7 +2235,7 @@
         <v>128539181</v>
       </c>
       <c r="B18" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 36342-2021 artfynd.xlsx
+++ b/artfynd/A 36342-2021 artfynd.xlsx
@@ -1066,7 +1066,7 @@
         <v>128539183</v>
       </c>
       <c r="B6" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128539191</v>
       </c>
       <c r="B8" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128539184</v>
       </c>
       <c r="B9" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128539186</v>
       </c>
       <c r="B10" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128539187</v>
       </c>
       <c r="B11" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128539190</v>
       </c>
       <c r="B12" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128539182</v>
       </c>
       <c r="B14" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>128539189</v>
       </c>
       <c r="B15" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128539188</v>
+        <v>128539177</v>
       </c>
       <c r="B16" t="n">
-        <v>98588</v>
+        <v>57849</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>725568</v>
+        <v>725639</v>
       </c>
       <c r="R16" t="n">
-        <v>7089783</v>
+        <v>7089856</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2135,32 +2135,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128539177</v>
+        <v>128539188</v>
       </c>
       <c r="B17" t="n">
-        <v>57849</v>
+        <v>98591</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>725639</v>
+        <v>725568</v>
       </c>
       <c r="R17" t="n">
-        <v>7089856</v>
+        <v>7089783</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2235,7 +2235,7 @@
         <v>128539181</v>
       </c>
       <c r="B18" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 36342-2021 artfynd.xlsx
+++ b/artfynd/A 36342-2021 artfynd.xlsx
@@ -1548,7 +1548,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128539187</v>
+        <v>128539190</v>
       </c>
       <c r="B11" t="n">
         <v>98591</v>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>725549</v>
+        <v>725646</v>
       </c>
       <c r="R11" t="n">
-        <v>7089797</v>
+        <v>7089766</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,7 +1645,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128539190</v>
+        <v>128539187</v>
       </c>
       <c r="B12" t="n">
         <v>98591</v>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>725646</v>
+        <v>725549</v>
       </c>
       <c r="R12" t="n">
-        <v>7089766</v>
+        <v>7089797</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128539177</v>
+        <v>128539188</v>
       </c>
       <c r="B16" t="n">
-        <v>57849</v>
+        <v>98591</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>725639</v>
+        <v>725568</v>
       </c>
       <c r="R16" t="n">
-        <v>7089856</v>
+        <v>7089783</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2135,32 +2135,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128539188</v>
+        <v>128539177</v>
       </c>
       <c r="B17" t="n">
-        <v>98591</v>
+        <v>57849</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>725568</v>
+        <v>725639</v>
       </c>
       <c r="R17" t="n">
-        <v>7089783</v>
+        <v>7089856</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 36342-2021 artfynd.xlsx
+++ b/artfynd/A 36342-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128539173</v>
       </c>
       <c r="B2" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128539172</v>
       </c>
       <c r="B4" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128539183</v>
       </c>
       <c r="B6" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128539191</v>
       </c>
       <c r="B8" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128539184</v>
       </c>
       <c r="B9" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128539186</v>
       </c>
       <c r="B10" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128539190</v>
+        <v>128539187</v>
       </c>
       <c r="B11" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>725646</v>
+        <v>725549</v>
       </c>
       <c r="R11" t="n">
-        <v>7089766</v>
+        <v>7089797</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128539187</v>
+        <v>128539190</v>
       </c>
       <c r="B12" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>725549</v>
+        <v>725646</v>
       </c>
       <c r="R12" t="n">
-        <v>7089797</v>
+        <v>7089766</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1745,7 +1745,7 @@
         <v>128539193</v>
       </c>
       <c r="B13" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128539182</v>
       </c>
       <c r="B14" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>128539189</v>
       </c>
       <c r="B15" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128539188</v>
+        <v>128539177</v>
       </c>
       <c r="B16" t="n">
-        <v>98591</v>
+        <v>57849</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>725568</v>
+        <v>725639</v>
       </c>
       <c r="R16" t="n">
-        <v>7089783</v>
+        <v>7089856</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2135,32 +2135,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128539177</v>
+        <v>128539188</v>
       </c>
       <c r="B17" t="n">
-        <v>57849</v>
+        <v>98592</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>725639</v>
+        <v>725568</v>
       </c>
       <c r="R17" t="n">
-        <v>7089856</v>
+        <v>7089783</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2235,7 +2235,7 @@
         <v>128539181</v>
       </c>
       <c r="B18" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 36342-2021 artfynd.xlsx
+++ b/artfynd/A 36342-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128539173</v>
       </c>
       <c r="B2" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128539178</v>
       </c>
       <c r="B3" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128539172</v>
       </c>
       <c r="B4" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128539194</v>
       </c>
       <c r="B5" t="n">
-        <v>82948</v>
+        <v>82975</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128539183</v>
       </c>
       <c r="B6" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128539171</v>
       </c>
       <c r="B7" t="n">
-        <v>75177</v>
+        <v>75204</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128539191</v>
       </c>
       <c r="B8" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128539184</v>
       </c>
       <c r="B9" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128539186</v>
       </c>
       <c r="B10" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128539187</v>
       </c>
       <c r="B11" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128539190</v>
       </c>
       <c r="B12" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128539193</v>
       </c>
       <c r="B13" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128539182</v>
       </c>
       <c r="B14" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>128539189</v>
       </c>
       <c r="B15" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>128539177</v>
       </c>
       <c r="B16" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>128539188</v>
       </c>
       <c r="B17" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>128539181</v>
       </c>
       <c r="B18" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>128539175</v>
       </c>
       <c r="B19" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>128539176</v>
       </c>
       <c r="B20" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>128539174</v>
       </c>
       <c r="B21" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 36342-2021 artfynd.xlsx
+++ b/artfynd/A 36342-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128539173</v>
       </c>
       <c r="B2" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128539178</v>
       </c>
       <c r="B3" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128539172</v>
       </c>
       <c r="B4" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128539194</v>
       </c>
       <c r="B5" t="n">
-        <v>82975</v>
+        <v>82979</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128539183</v>
       </c>
       <c r="B6" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128539171</v>
       </c>
       <c r="B7" t="n">
-        <v>75204</v>
+        <v>75205</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128539191</v>
       </c>
       <c r="B8" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128539184</v>
       </c>
       <c r="B9" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128539186</v>
       </c>
       <c r="B10" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128539187</v>
       </c>
       <c r="B11" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128539190</v>
       </c>
       <c r="B12" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128539193</v>
       </c>
       <c r="B13" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128539182</v>
       </c>
       <c r="B14" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>128539189</v>
       </c>
       <c r="B15" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>128539188</v>
       </c>
       <c r="B17" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>128539181</v>
       </c>
       <c r="B18" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 36342-2021 artfynd.xlsx
+++ b/artfynd/A 36342-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128539173</v>
       </c>
       <c r="B2" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128539172</v>
+        <v>128539194</v>
       </c>
       <c r="B4" t="n">
-        <v>91499</v>
+        <v>82979</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>725582</v>
+        <v>725726</v>
       </c>
       <c r="R4" t="n">
-        <v>7089761</v>
+        <v>7089844</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128539194</v>
+        <v>128539172</v>
       </c>
       <c r="B5" t="n">
-        <v>82979</v>
+        <v>91504</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>725726</v>
+        <v>725582</v>
       </c>
       <c r="R5" t="n">
-        <v>7089844</v>
+        <v>7089761</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
         <v>128539183</v>
       </c>
       <c r="B6" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128539191</v>
       </c>
       <c r="B8" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128539184</v>
       </c>
       <c r="B9" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128539186</v>
       </c>
       <c r="B10" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128539187</v>
       </c>
       <c r="B11" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128539190</v>
       </c>
       <c r="B12" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128539193</v>
       </c>
       <c r="B13" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128539182</v>
       </c>
       <c r="B14" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>128539189</v>
       </c>
       <c r="B15" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>128539188</v>
       </c>
       <c r="B17" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>128539181</v>
       </c>
       <c r="B18" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 36342-2021 artfynd.xlsx
+++ b/artfynd/A 36342-2021 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128539194</v>
+        <v>128539172</v>
       </c>
       <c r="B4" t="n">
-        <v>82979</v>
+        <v>91504</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>725726</v>
+        <v>725582</v>
       </c>
       <c r="R4" t="n">
-        <v>7089844</v>
+        <v>7089761</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128539172</v>
+        <v>128539194</v>
       </c>
       <c r="B5" t="n">
-        <v>91504</v>
+        <v>82979</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>725582</v>
+        <v>725726</v>
       </c>
       <c r="R5" t="n">
-        <v>7089761</v>
+        <v>7089844</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1742,45 +1742,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128539193</v>
+        <v>128539182</v>
       </c>
       <c r="B13" t="n">
-        <v>91522</v>
+        <v>98632</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Storbäcken, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>725525</v>
+        <v>725674</v>
       </c>
       <c r="R13" t="n">
-        <v>7089765</v>
+        <v>7089751</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1821,6 +1825,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1839,7 +1844,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128539182</v>
+        <v>128539189</v>
       </c>
       <c r="B14" t="n">
         <v>98632</v>
@@ -1867,21 +1872,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Storbäcken, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>725674</v>
+        <v>725622</v>
       </c>
       <c r="R14" t="n">
-        <v>7089751</v>
+        <v>7089767</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1922,7 +1923,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1941,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128539189</v>
+        <v>128539193</v>
       </c>
       <c r="B15" t="n">
-        <v>98632</v>
+        <v>91522</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>725622</v>
+        <v>725525</v>
       </c>
       <c r="R15" t="n">
-        <v>7089767</v>
+        <v>7089765</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 36342-2021 artfynd.xlsx
+++ b/artfynd/A 36342-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128539173</v>
       </c>
       <c r="B2" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128539178</v>
       </c>
       <c r="B3" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128539172</v>
       </c>
       <c r="B4" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128539194</v>
       </c>
       <c r="B5" t="n">
-        <v>82979</v>
+        <v>82983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128539183</v>
       </c>
       <c r="B6" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128539171</v>
       </c>
       <c r="B7" t="n">
-        <v>75205</v>
+        <v>75209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128539191</v>
       </c>
       <c r="B8" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128539184</v>
       </c>
       <c r="B9" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128539186</v>
       </c>
       <c r="B10" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128539187</v>
       </c>
       <c r="B11" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128539190</v>
       </c>
       <c r="B12" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128539182</v>
       </c>
       <c r="B13" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>128539189</v>
       </c>
       <c r="B14" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>128539193</v>
       </c>
       <c r="B15" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128539177</v>
+        <v>128539188</v>
       </c>
       <c r="B16" t="n">
-        <v>57876</v>
+        <v>98636</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>725639</v>
+        <v>725568</v>
       </c>
       <c r="R16" t="n">
-        <v>7089856</v>
+        <v>7089783</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2135,32 +2135,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128539188</v>
+        <v>128539177</v>
       </c>
       <c r="B17" t="n">
-        <v>98632</v>
+        <v>57880</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>725568</v>
+        <v>725639</v>
       </c>
       <c r="R17" t="n">
-        <v>7089783</v>
+        <v>7089856</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2235,7 +2235,7 @@
         <v>128539181</v>
       </c>
       <c r="B18" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>128539175</v>
       </c>
       <c r="B19" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>128539176</v>
       </c>
       <c r="B20" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>128539174</v>
       </c>
       <c r="B21" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 36342-2021 artfynd.xlsx
+++ b/artfynd/A 36342-2021 artfynd.xlsx
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128539188</v>
+        <v>128539177</v>
       </c>
       <c r="B16" t="n">
-        <v>98636</v>
+        <v>57880</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>725568</v>
+        <v>725639</v>
       </c>
       <c r="R16" t="n">
-        <v>7089783</v>
+        <v>7089856</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2135,32 +2135,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128539177</v>
+        <v>128539188</v>
       </c>
       <c r="B17" t="n">
-        <v>57880</v>
+        <v>98636</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>725639</v>
+        <v>725568</v>
       </c>
       <c r="R17" t="n">
-        <v>7089856</v>
+        <v>7089783</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 36342-2021 artfynd.xlsx
+++ b/artfynd/A 36342-2021 artfynd.xlsx
@@ -1548,7 +1548,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128539187</v>
+        <v>128539190</v>
       </c>
       <c r="B11" t="n">
         <v>98636</v>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>725549</v>
+        <v>725646</v>
       </c>
       <c r="R11" t="n">
-        <v>7089797</v>
+        <v>7089766</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,7 +1645,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128539190</v>
+        <v>128539187</v>
       </c>
       <c r="B12" t="n">
         <v>98636</v>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>725646</v>
+        <v>725549</v>
       </c>
       <c r="R12" t="n">
-        <v>7089766</v>
+        <v>7089797</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,49 +1742,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128539182</v>
+        <v>128539193</v>
       </c>
       <c r="B13" t="n">
-        <v>98636</v>
+        <v>91526</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Storbäcken, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>725674</v>
+        <v>725525</v>
       </c>
       <c r="R13" t="n">
-        <v>7089751</v>
+        <v>7089765</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1825,7 +1821,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1844,7 +1839,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128539189</v>
+        <v>128539182</v>
       </c>
       <c r="B14" t="n">
         <v>98636</v>
@@ -1872,17 +1867,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Storbäcken, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>725622</v>
+        <v>725674</v>
       </c>
       <c r="R14" t="n">
-        <v>7089767</v>
+        <v>7089751</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1923,6 +1922,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1941,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128539193</v>
+        <v>128539189</v>
       </c>
       <c r="B15" t="n">
-        <v>91526</v>
+        <v>98636</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>725525</v>
+        <v>725622</v>
       </c>
       <c r="R15" t="n">
-        <v>7089765</v>
+        <v>7089767</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 36342-2021 artfynd.xlsx
+++ b/artfynd/A 36342-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128539173</v>
       </c>
       <c r="B2" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128539178</v>
       </c>
       <c r="B3" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128539172</v>
       </c>
       <c r="B4" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128539194</v>
       </c>
       <c r="B5" t="n">
-        <v>82983</v>
+        <v>82892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128539183</v>
       </c>
       <c r="B6" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128539171</v>
       </c>
       <c r="B7" t="n">
-        <v>75209</v>
+        <v>83005</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128539191</v>
       </c>
       <c r="B8" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128539184</v>
       </c>
       <c r="B9" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128539186</v>
       </c>
       <c r="B10" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128539190</v>
+        <v>128539187</v>
       </c>
       <c r="B11" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>725646</v>
+        <v>725549</v>
       </c>
       <c r="R11" t="n">
-        <v>7089766</v>
+        <v>7089797</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128539187</v>
+        <v>128539190</v>
       </c>
       <c r="B12" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>725549</v>
+        <v>725646</v>
       </c>
       <c r="R12" t="n">
-        <v>7089797</v>
+        <v>7089766</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1745,7 +1745,7 @@
         <v>128539193</v>
       </c>
       <c r="B13" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128539182</v>
       </c>
       <c r="B14" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>128539189</v>
       </c>
       <c r="B15" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>128539177</v>
       </c>
       <c r="B16" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>128539188</v>
       </c>
       <c r="B17" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>128539181</v>
       </c>
       <c r="B18" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>128539175</v>
       </c>
       <c r="B19" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>128539176</v>
       </c>
       <c r="B20" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>128539174</v>
       </c>
       <c r="B21" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 36342-2021 artfynd.xlsx
+++ b/artfynd/A 36342-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128539173</v>
       </c>
       <c r="B2" t="n">
-        <v>91515</v>
+        <v>91520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128539178</v>
       </c>
       <c r="B3" t="n">
-        <v>80163</v>
+        <v>80168</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128539194</v>
+        <v>128539172</v>
       </c>
       <c r="B4" t="n">
-        <v>82892</v>
+        <v>91520</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>725726</v>
+        <v>725582</v>
       </c>
       <c r="R4" t="n">
-        <v>7089844</v>
+        <v>7089761</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128539172</v>
+        <v>128539194</v>
       </c>
       <c r="B5" t="n">
-        <v>91515</v>
+        <v>82897</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>725582</v>
+        <v>725726</v>
       </c>
       <c r="R5" t="n">
-        <v>7089761</v>
+        <v>7089844</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
         <v>128539183</v>
       </c>
       <c r="B6" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128539171</v>
       </c>
       <c r="B7" t="n">
-        <v>83005</v>
+        <v>83010</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128539191</v>
       </c>
       <c r="B8" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128539184</v>
       </c>
       <c r="B9" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128539186</v>
       </c>
       <c r="B10" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128539187</v>
       </c>
       <c r="B11" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128539190</v>
       </c>
       <c r="B12" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128539193</v>
       </c>
       <c r="B13" t="n">
-        <v>91533</v>
+        <v>91538</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128539182</v>
       </c>
       <c r="B14" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>128539189</v>
       </c>
       <c r="B15" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128539177</v>
+        <v>128539188</v>
       </c>
       <c r="B16" t="n">
-        <v>57883</v>
+        <v>98651</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>725639</v>
+        <v>725568</v>
       </c>
       <c r="R16" t="n">
-        <v>7089856</v>
+        <v>7089783</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2135,32 +2135,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128539188</v>
+        <v>128539177</v>
       </c>
       <c r="B17" t="n">
-        <v>98646</v>
+        <v>57883</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>725568</v>
+        <v>725639</v>
       </c>
       <c r="R17" t="n">
-        <v>7089783</v>
+        <v>7089856</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2235,7 +2235,7 @@
         <v>128539181</v>
       </c>
       <c r="B18" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 36342-2021 artfynd.xlsx
+++ b/artfynd/A 36342-2021 artfynd.xlsx
@@ -1742,45 +1742,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128539193</v>
+        <v>128539182</v>
       </c>
       <c r="B13" t="n">
-        <v>91538</v>
+        <v>98651</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Storbäcken, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>725525</v>
+        <v>725674</v>
       </c>
       <c r="R13" t="n">
-        <v>7089765</v>
+        <v>7089751</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1821,6 +1825,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1839,7 +1844,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128539182</v>
+        <v>128539189</v>
       </c>
       <c r="B14" t="n">
         <v>98651</v>
@@ -1867,21 +1872,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Storbäcken, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>725674</v>
+        <v>725622</v>
       </c>
       <c r="R14" t="n">
-        <v>7089751</v>
+        <v>7089767</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1922,7 +1923,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1941,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128539189</v>
+        <v>128539193</v>
       </c>
       <c r="B15" t="n">
-        <v>98651</v>
+        <v>91538</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>725622</v>
+        <v>725525</v>
       </c>
       <c r="R15" t="n">
-        <v>7089767</v>
+        <v>7089765</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128539188</v>
+        <v>128539177</v>
       </c>
       <c r="B16" t="n">
-        <v>98651</v>
+        <v>57883</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>725568</v>
+        <v>725639</v>
       </c>
       <c r="R16" t="n">
-        <v>7089783</v>
+        <v>7089856</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2135,32 +2135,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128539177</v>
+        <v>128539188</v>
       </c>
       <c r="B17" t="n">
-        <v>57883</v>
+        <v>98651</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>725639</v>
+        <v>725568</v>
       </c>
       <c r="R17" t="n">
-        <v>7089856</v>
+        <v>7089783</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 36342-2021 artfynd.xlsx
+++ b/artfynd/A 36342-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128539173</v>
       </c>
       <c r="B2" t="n">
-        <v>91520</v>
+        <v>91526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128539178</v>
       </c>
       <c r="B3" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128539172</v>
       </c>
       <c r="B4" t="n">
-        <v>91520</v>
+        <v>91526</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128539194</v>
       </c>
       <c r="B5" t="n">
-        <v>82897</v>
+        <v>82898</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128539183</v>
       </c>
       <c r="B6" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128539171</v>
       </c>
       <c r="B7" t="n">
-        <v>83010</v>
+        <v>83011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128539191</v>
       </c>
       <c r="B8" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128539184</v>
       </c>
       <c r="B9" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128539186</v>
       </c>
       <c r="B10" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128539187</v>
       </c>
       <c r="B11" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128539190</v>
       </c>
       <c r="B12" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1742,49 +1742,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128539182</v>
+        <v>128539193</v>
       </c>
       <c r="B13" t="n">
-        <v>98651</v>
+        <v>91544</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Storbäcken, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>725674</v>
+        <v>725525</v>
       </c>
       <c r="R13" t="n">
-        <v>7089751</v>
+        <v>7089765</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1825,7 +1821,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1844,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128539189</v>
+        <v>128539182</v>
       </c>
       <c r="B14" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1872,17 +1867,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Storbäcken, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>725622</v>
+        <v>725674</v>
       </c>
       <c r="R14" t="n">
-        <v>7089767</v>
+        <v>7089751</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1923,6 +1922,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1941,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128539193</v>
+        <v>128539189</v>
       </c>
       <c r="B15" t="n">
-        <v>91538</v>
+        <v>98659</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>725525</v>
+        <v>725622</v>
       </c>
       <c r="R15" t="n">
-        <v>7089765</v>
+        <v>7089767</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128539177</v>
+        <v>128539188</v>
       </c>
       <c r="B16" t="n">
-        <v>57883</v>
+        <v>98659</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>725639</v>
+        <v>725568</v>
       </c>
       <c r="R16" t="n">
-        <v>7089856</v>
+        <v>7089783</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2135,32 +2135,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128539188</v>
+        <v>128539177</v>
       </c>
       <c r="B17" t="n">
-        <v>98651</v>
+        <v>57883</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>725568</v>
+        <v>725639</v>
       </c>
       <c r="R17" t="n">
-        <v>7089783</v>
+        <v>7089856</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2235,7 +2235,7 @@
         <v>128539181</v>
       </c>
       <c r="B18" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
